--- a/fixtures/export/test1-成绩导出.xlsx
+++ b/fixtures/export/test1-成绩导出.xlsx
@@ -6,17 +6,21 @@
   <sheets>
     <sheet sheetId="1" name="成绩汇总" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="答题明细" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="填空题明细" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
   <si>
     <t>姓名</t>
   </si>
   <si>
+    <t>单位</t>
+  </si>
+  <si>
     <t>身份证号</t>
   </si>
   <si>
@@ -38,6 +42,9 @@
     <t>示例学生</t>
   </si>
   <si>
+    <t>示例单位</t>
+  </si>
+  <si>
     <t>110101********1234</t>
   </si>
   <si>
@@ -63,6 +70,24 @@
   </si>
   <si>
     <t>得分</t>
+  </si>
+  <si>
+    <t>题序</t>
+  </si>
+  <si>
+    <t>答题卡题号</t>
+  </si>
+  <si>
+    <t>空位</t>
+  </si>
+  <si>
+    <t>学员作答</t>
+  </si>
+  <si>
+    <t>参考答案</t>
+  </si>
+  <si>
+    <t>满分</t>
   </si>
 </sst>
 </file>
@@ -443,18 +468,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="7" width="10" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="10" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="7" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -476,27 +502,33 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
-        <v>9</v>
-      </c>
       <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2">
+        <v>11</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
         <v>2</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>1</v>
       </c>
     </row>
@@ -508,18 +540,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="5" max="6" width="16" customWidth="1"/>
-    <col min="7" max="8" width="8" customWidth="1"/>
+    <col min="1" max="9" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -527,22 +554,74 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="11" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
